--- a/data/trans_dic/IP44C$hipoteca_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$hipoteca_2023-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que han tenido, al menos, algún retraso en el pago de la hipoteca</t>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de la hipoteca (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,91</t>
+          <t>0,0; 3,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,16</t>
+          <t>0,47; 4,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,85</t>
+          <t>0,35; 2,52</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,03</t>
+          <t>0,0; 6,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 6,58</t>
+          <t>1,2; 6,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 5,03</t>
+          <t>1,1; 5,31</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,58</t>
+          <t>0,0; 6,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,97</t>
+          <t>0,0; 6,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,93</t>
+          <t>0,31; 3,94</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,53</t>
+          <t>0,0; 2,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 4,08</t>
+          <t>0,35; 3,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,41</t>
+          <t>0,32; 2,37</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,57</t>
+          <t>0,0; 3,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,08</t>
+          <t>0,0; 4,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,44</t>
+          <t>0,5; 3,38</t>
         </is>
       </c>
     </row>
@@ -821,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,75</t>
+          <t>0,0; 8,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,81</t>
+          <t>0,0; 4,12</t>
         </is>
       </c>
     </row>
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,1</t>
+          <t>0,55; 2,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,63</t>
+          <t>0,95; 2,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,0</t>
+          <t>0,9; 2,01</t>
         </is>
       </c>
     </row>
@@ -905,4 +906,602 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de la hipoteca (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2209</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2719</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3160</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>632; 6183</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>817; 5973</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1743</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2951</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4694</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 6137</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1151; 6676</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2086; 10111</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1084</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1528</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3286</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3862</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>358; 4554</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1379</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2633</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4012</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5658</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>749; 7884</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1352; 10138</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1134</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2771</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3906</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3826</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 7706</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1344; 9167</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1898</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1898</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5860</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5571</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>7107</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>11648</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>18756</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>3527; 12991</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>6918; 18379</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>12416; 27701</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP44C$hipoteca_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$hipoteca_2023-Clase-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,07</t>
+          <t>0,0; 2,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,62</t>
+          <t>0,52; 4,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,52</t>
+          <t>0,41; 2,64</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,48</t>
+          <t>0,0; 6,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 6,99</t>
+          <t>1,2; 7,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 5,31</t>
+          <t>1,0; 5,05</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,34</t>
+          <t>0,0; 6,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,05</t>
+          <t>0,0; 6,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,94</t>
+          <t>0,32; 3,59</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,64</t>
+          <t>0,0; 2,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,71</t>
+          <t>0,36; 3,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,37</t>
+          <t>0,34; 2,22</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,34</t>
+          <t>0,0; 3,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,91</t>
+          <t>0,52; 4,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,38</t>
+          <t>0,54; 3,24</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,82</t>
+          <t>0,0; 9,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,12</t>
+          <t>0,0; 4,44</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,02</t>
+          <t>0,57; 2,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,51</t>
+          <t>0,95; 2,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,01</t>
+          <t>0,88; 2,0</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3160</t>
+          <t>0; 2476</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>632; 6183</t>
+          <t>695; 5749</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>817; 5973</t>
+          <t>969; 6247</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6137</t>
+          <t>0; 5883</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1151; 6676</t>
+          <t>1150; 6834</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2086; 10111</t>
+          <t>1901; 9605</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3286</t>
+          <t>0; 3268</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3862</t>
+          <t>0; 4209</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>358; 4554</t>
+          <t>374; 4150</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5658</t>
+          <t>0; 5241</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>749; 7884</t>
+          <t>774; 8309</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1352; 10138</t>
+          <t>1436; 9474</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3826</t>
+          <t>0; 4320</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 7706</t>
+          <t>811; 7418</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1344; 9167</t>
+          <t>1453; 8784</t>
         </is>
       </c>
     </row>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5860</t>
+          <t>0; 6373</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5571</t>
+          <t>0; 6012</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3527; 12991</t>
+          <t>3645; 12951</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6918; 18379</t>
+          <t>6934; 19128</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12416; 27701</t>
+          <t>12122; 27582</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$hipoteca_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$hipoteca_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,41</t>
+          <t>0,51; 4,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,3</t>
+          <t>0,0; 2,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,64</t>
+          <t>0,39; 3,02</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,21</t>
+          <t>1,05; 6,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 7,15</t>
+          <t>0,0; 6,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,05</t>
+          <t>0,93; 4,86</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,3</t>
+          <t>0,0; 6,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,59</t>
+          <t>0,0; 4,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,59</t>
+          <t>0,24; 3,41</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,45</t>
+          <t>0,34; 4,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,91</t>
+          <t>0,0; 3,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,22</t>
+          <t>0,35; 2,71</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>0,99%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,77</t>
+          <t>0,63; 5,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,73</t>
+          <t>0,0; 3,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,24</t>
+          <t>0,52; 3,79</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 10,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,44</t>
+          <t>0,0; 5,38</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,01</t>
+          <t>0,96; 2,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,61</t>
+          <t>0,6; 2,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,0</t>
+          <t>0,96; 2,17</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>2143</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2209</t>
+          <t>450</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2719</t>
+          <t>2593</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2476</t>
+          <t>610; 5567</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>695; 5749</t>
+          <t>0; 2712</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>969; 6247</t>
+          <t>870; 6674</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1743</t>
+          <t>2546</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>1873</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>4419</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5883</t>
+          <t>961; 5598</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1150; 6834</t>
+          <t>0; 6231</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1901; 9605</t>
+          <t>1750; 9143</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>849</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>385</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1528</t>
+          <t>1234</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3268</t>
+          <t>0; 3513</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4209</t>
+          <t>0; 2571</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>374; 4150</t>
+          <t>267; 3770</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>2541</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2633</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>3945</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5241</t>
+          <t>663; 8997</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>774; 8309</t>
+          <t>0; 5850</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1436; 9474</t>
+          <t>1307; 10087</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>2837</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2771</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3962</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4320</t>
+          <t>892; 8030</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>811; 7418</t>
+          <t>0; 4284</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1453; 8784</t>
+          <t>1342; 9696</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2093</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>2093</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6373</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 7196</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 6012</t>
+          <t>0; 7190</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>10917</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>11648</t>
+          <t>7328</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18756</t>
+          <t>18245</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3645; 12951</t>
+          <t>6473; 18273</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6934; 19128</t>
+          <t>3636; 13906</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12122; 27582</t>
+          <t>12355; 27806</t>
         </is>
       </c>
     </row>
